--- a/cet4/result/17_校园甜宠_霸道学长的追妻路/17_校园甜宠_霸道学长的追妻路_学习版.xlsx
+++ b/cet4/result/17_校园甜宠_霸道学长的追妻路/17_校园甜宠_霸道学长的追妻路_学习版.xlsx
@@ -397,801 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>June</v>
       </c>
       <c r="B2" t="str">
-        <v>June</v>
+        <v>/dʒuːn/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>六月</v>
       </c>
-      <c r="D2" t="str">
-        <v>June(六月)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>weekend</v>
       </c>
       <c r="B3" t="str">
-        <v>weekend</v>
+        <v>/ˈwiːkend/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vi./adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>周末</v>
       </c>
-      <c r="D3" t="str">
-        <v>weekend(周末)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>academic</v>
       </c>
       <c r="B4" t="str">
-        <v>academic</v>
+        <v>/ˌækəˈdemɪk/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>学术的</v>
       </c>
-      <c r="D4" t="str">
-        <v>academic(学术的)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>first</v>
       </c>
       <c r="B5" t="str">
-        <v>first</v>
+        <v>/fɜːrst/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./v./adj./adv./num.</v>
+      </c>
+      <c r="D5" t="str">
         <v>第一</v>
       </c>
-      <c r="D5" t="str">
-        <v>first(第一)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>shade</v>
       </c>
       <c r="B6" t="str">
-        <v>shade</v>
+        <v>/ʃeɪd/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>阴影</v>
       </c>
-      <c r="D6" t="str">
-        <v>shade(阴影)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>edition</v>
       </c>
       <c r="B7" t="str">
-        <v>edition</v>
+        <v>/ɪˈdɪʃn/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>版本</v>
       </c>
-      <c r="D7" t="str">
-        <v>edition(版本)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>hook</v>
       </c>
       <c r="B8" t="str">
-        <v>hook</v>
+        <v>/hʊk/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D8" t="str">
         <v>挂钩</v>
       </c>
-      <c r="D8" t="str">
-        <v>hook(挂钩)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>microcomputer</v>
       </c>
       <c r="B9" t="str">
-        <v>microcomputer</v>
+        <v>/ˈmaɪkroʊkəmpjuːtər/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>微电脑</v>
       </c>
-      <c r="D9" t="str">
-        <v>microcomputer(微电脑)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>curiosity</v>
       </c>
       <c r="B10" t="str">
-        <v>curiosity</v>
+        <v>/ˌkjʊriˈɑːsəti/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>好奇心</v>
       </c>
-      <c r="D10" t="str">
-        <v>curiosity(好奇心)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>finish</v>
       </c>
       <c r="B11" t="str">
-        <v>finish</v>
+        <v>/ˈfɪnɪʃ/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D11" t="str">
         <v>完成</v>
       </c>
-      <c r="D11" t="str">
-        <v>finish(完成)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>industrialize</v>
       </c>
       <c r="B12" t="str">
-        <v>industrialize</v>
+        <v>/ɪnˈdʌstriəlaɪz/</v>
       </c>
       <c r="C12" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D12" t="str">
         <v>工业化</v>
       </c>
-      <c r="D12" t="str">
-        <v>industrialize(工业化)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>existence</v>
       </c>
       <c r="B13" t="str">
-        <v>existence</v>
+        <v>/ɪɡˈzɪstəns/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>存在</v>
       </c>
-      <c r="D13" t="str">
-        <v>existence(存在)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>springtime</v>
       </c>
       <c r="B14" t="str">
-        <v>springtime</v>
+        <v>/ˈsprɪŋtaɪm/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>春天</v>
       </c>
-      <c r="D14" t="str">
-        <v>springtime(春天)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>secretary</v>
       </c>
       <c r="B15" t="str">
-        <v>secretary</v>
+        <v>/ˈsekrəteri/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>秘书</v>
       </c>
-      <c r="D15" t="str">
-        <v>secretary(秘书)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>popular</v>
       </c>
       <c r="B16" t="str">
-        <v>popular</v>
+        <v>/ˈpɑːpjələr/</v>
       </c>
       <c r="C16" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>流行的</v>
       </c>
-      <c r="D16" t="str">
-        <v>popular(流行的)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>writer</v>
       </c>
       <c r="B17" t="str">
-        <v>writer</v>
+        <v>/ˈraɪtər/</v>
       </c>
       <c r="C17" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>作家</v>
       </c>
-      <c r="D17" t="str">
-        <v>writer(作家)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>entrance</v>
       </c>
       <c r="B18" t="str">
-        <v>entrance</v>
+        <v>/ɪnˈtrɑ:ns;ˈentrəns/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D18" t="str">
         <v>入口</v>
       </c>
-      <c r="D18" t="str">
-        <v>entrance(入口)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>logical</v>
       </c>
       <c r="B19" t="str">
-        <v>logical</v>
+        <v>/ˈlɑːdʒɪkl/</v>
       </c>
       <c r="C19" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>合逻辑的</v>
       </c>
-      <c r="D19" t="str">
-        <v>logical(合逻辑的)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>troop</v>
       </c>
       <c r="B20" t="str">
-        <v>troop</v>
+        <v>/truːp/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D20" t="str">
         <v>军队</v>
       </c>
-      <c r="D20" t="str">
-        <v>troop(军队)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>rare</v>
       </c>
       <c r="B21" t="str">
-        <v>rare</v>
+        <v>/rer/</v>
       </c>
       <c r="C21" t="str">
+        <v>vi./v./adj./adv.</v>
+      </c>
+      <c r="D21" t="str">
         <v>稀有的</v>
       </c>
-      <c r="D21" t="str">
-        <v>rare(稀有的)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>preparation</v>
       </c>
       <c r="B22" t="str">
-        <v>preparation</v>
+        <v>/ˌprepəˈreɪʃn/</v>
       </c>
       <c r="C22" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>准备</v>
       </c>
-      <c r="D22" t="str">
-        <v>preparation(准备)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>scream</v>
       </c>
       <c r="B23" t="str">
-        <v>scream</v>
+        <v>/skriːm/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D23" t="str">
         <v>尖叫</v>
       </c>
-      <c r="D23" t="str">
-        <v>scream(尖叫)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>significant</v>
       </c>
       <c r="B24" t="str">
-        <v>significant</v>
+        <v>/sɪɡˈnɪfɪkənt/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D24" t="str">
         <v>重大的</v>
       </c>
-      <c r="D24" t="str">
-        <v>significant(重大的)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>early</v>
       </c>
       <c r="B25" t="str">
-        <v>early</v>
+        <v>/ˈɜːrli/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D25" t="str">
         <v>早期的</v>
       </c>
-      <c r="D25" t="str">
-        <v>early(早期的)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>east</v>
       </c>
       <c r="B26" t="str">
-        <v>east</v>
+        <v>/iːst/</v>
       </c>
       <c r="C26" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D26" t="str">
         <v>东方</v>
       </c>
-      <c r="D26" t="str">
-        <v>east(东方)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>already</v>
       </c>
       <c r="B27" t="str">
-        <v>already</v>
+        <v>/ɔːlˈredi/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D27" t="str">
         <v>已经</v>
       </c>
-      <c r="D27" t="str">
-        <v>already(已经)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>take</v>
       </c>
       <c r="B28" t="str">
-        <v>take</v>
+        <v>/teɪk/</v>
       </c>
       <c r="C28" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D28" t="str">
         <v>拿</v>
       </c>
-      <c r="D28" t="str">
-        <v>take(拿)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>pursue</v>
       </c>
       <c r="B29" t="str">
-        <v>pursue</v>
+        <v>/pərˈsuː/</v>
       </c>
       <c r="C29" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D29" t="str">
         <v>追求</v>
       </c>
-      <c r="D29" t="str">
-        <v>pursue(追求)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>sandwich</v>
       </c>
       <c r="B30" t="str">
-        <v>sandwich</v>
+        <v>/ˈsænwɪtʃ/</v>
       </c>
       <c r="C30" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D30" t="str">
         <v>三明治</v>
       </c>
-      <c r="D30" t="str">
-        <v>sandwich(三明治)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>labor</v>
       </c>
       <c r="B31" t="str">
-        <v>labor</v>
+        <v>/ˈleɪbər/</v>
       </c>
       <c r="C31" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D31" t="str">
         <v>劳动</v>
       </c>
-      <c r="D31" t="str">
-        <v>labor(劳动)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>behave</v>
       </c>
       <c r="B32" t="str">
-        <v>behave</v>
+        <v>/bɪˈheɪv/</v>
       </c>
       <c r="C32" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D32" t="str">
         <v>表现</v>
       </c>
-      <c r="D32" t="str">
-        <v>behave(表现)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>avoid</v>
       </c>
       <c r="B33" t="str">
-        <v>avoid</v>
+        <v>/əˈvɔɪd/</v>
       </c>
       <c r="C33" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D33" t="str">
         <v>避免</v>
       </c>
-      <c r="D33" t="str">
-        <v>avoid(避免)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>incline</v>
       </c>
       <c r="B34" t="str">
-        <v>incline</v>
+        <v>/ɪnˈklaɪn/</v>
       </c>
       <c r="C34" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D34" t="str">
         <v>倾向</v>
       </c>
-      <c r="D34" t="str">
-        <v>incline(倾向)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>badminton</v>
       </c>
       <c r="B35" t="str">
-        <v>badminton</v>
+        <v>/ˈbædmɪntən/</v>
       </c>
       <c r="C35" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>羽毛球</v>
       </c>
-      <c r="D35" t="str">
-        <v>badminton(羽毛球)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>Australian</v>
       </c>
       <c r="B36" t="str">
-        <v>Australian</v>
+        <v>/ɔːˈstreɪliən/</v>
       </c>
       <c r="C36" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D36" t="str">
         <v>澳大利亚的</v>
       </c>
-      <c r="D36" t="str">
-        <v>Australian(澳大利亚的)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>bud</v>
       </c>
       <c r="B37" t="str">
-        <v>bud</v>
+        <v>/bʌd/</v>
       </c>
       <c r="C37" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D37" t="str">
         <v>芽</v>
       </c>
-      <c r="D37" t="str">
-        <v>bud(芽)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>Brazilian</v>
       </c>
       <c r="B38" t="str">
-        <v>hook</v>
+        <v>/brəˈzɪliən/</v>
       </c>
       <c r="C38" t="str">
-        <v>钩住</v>
+        <v>n./adj.</v>
       </c>
       <c r="D38" t="str">
-        <v>hook(钩住)📢</v>
+        <v>巴西的</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>slender</v>
       </c>
       <c r="B39" t="str">
-        <v>behave</v>
+        <v>/ˈslendər/</v>
       </c>
       <c r="C39" t="str">
-        <v>表现</v>
+        <v>adj.</v>
       </c>
       <c r="D39" t="str">
-        <v>behave(表现)📢</v>
+        <v>苗条的</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>singer</v>
       </c>
       <c r="B40" t="str">
-        <v>Brazilian</v>
+        <v>/ˈsɪŋər/</v>
       </c>
       <c r="C40" t="str">
-        <v>巴西的</v>
+        <v>n.</v>
       </c>
       <c r="D40" t="str">
-        <v>Brazilian(巴西的)📢</v>
+        <v>歌手</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>noun</v>
       </c>
       <c r="B41" t="str">
-        <v>slender</v>
+        <v>/naʊn/</v>
       </c>
       <c r="C41" t="str">
-        <v>苗条的</v>
+        <v>n.</v>
       </c>
       <c r="D41" t="str">
-        <v>slender(苗条的)📢</v>
+        <v>名词</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>criticism</v>
       </c>
       <c r="B42" t="str">
-        <v>singer</v>
+        <v>/ˈkrɪtɪsɪzəm/</v>
       </c>
       <c r="C42" t="str">
-        <v>歌手</v>
+        <v>n.</v>
       </c>
       <c r="D42" t="str">
-        <v>singer(歌手)📢</v>
+        <v>批评</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>happiness</v>
       </c>
       <c r="B43" t="str">
-        <v>noun</v>
+        <v>/ˈhæpinəs/</v>
       </c>
       <c r="C43" t="str">
-        <v>名词</v>
+        <v>n.</v>
       </c>
       <c r="D43" t="str">
-        <v>noun(名词)📢</v>
+        <v>幸福</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>free</v>
       </c>
       <c r="B44" t="str">
-        <v>scream</v>
+        <v>/friː/</v>
       </c>
       <c r="C44" t="str">
-        <v>尖叫</v>
+        <v>n./vt./v./adj./adv.</v>
       </c>
       <c r="D44" t="str">
-        <v>scream(尖叫)📢</v>
+        <v>自由的</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>kneel</v>
       </c>
       <c r="B45" t="str">
-        <v>criticism</v>
+        <v>/niːl/</v>
       </c>
       <c r="C45" t="str">
-        <v>批评</v>
+        <v>vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>criticism(批评)📢</v>
+        <v>跪下</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>under</v>
       </c>
       <c r="B46" t="str">
-        <v>already</v>
+        <v>/ˈʌndər/</v>
       </c>
       <c r="C46" t="str">
-        <v>已经</v>
+        <v>v./adv./prep.</v>
       </c>
       <c r="D46" t="str">
-        <v>already(已经)📢</v>
+        <v>在...之下</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>invasion</v>
       </c>
       <c r="B47" t="str">
-        <v>happiness</v>
+        <v>/ɪnˈveɪʒn/</v>
       </c>
       <c r="C47" t="str">
-        <v>幸福</v>
+        <v>n.</v>
       </c>
       <c r="D47" t="str">
-        <v>happiness(幸福)📢</v>
+        <v>入侵</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>wake</v>
       </c>
       <c r="B48" t="str">
-        <v>free</v>
+        <v>/weɪk/</v>
       </c>
       <c r="C48" t="str">
-        <v>自由的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D48" t="str">
-        <v>free(自由的)📢</v>
+        <v>唤醒</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>dream</v>
       </c>
       <c r="B49" t="str">
-        <v>kneel</v>
+        <v>/driːm/</v>
       </c>
       <c r="C49" t="str">
-        <v>跪下</v>
+        <v>n./v./adj.</v>
       </c>
       <c r="D49" t="str">
-        <v>kneel(跪下)📢</v>
+        <v>梦想</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>mechanics</v>
       </c>
       <c r="B50" t="str">
-        <v>under</v>
+        <v>/məˈkænɪks/</v>
       </c>
       <c r="C50" t="str">
-        <v>在...之下</v>
+        <v>n.</v>
       </c>
       <c r="D50" t="str">
-        <v>under(在...之下)📢</v>
+        <v>力学</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>substance</v>
       </c>
       <c r="B51" t="str">
-        <v>happiness</v>
+        <v>/ˈsʌbstəns/</v>
       </c>
       <c r="C51" t="str">
-        <v>幸福</v>
+        <v>n.</v>
       </c>
       <c r="D51" t="str">
-        <v>happiness(幸福)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>invasion</v>
-      </c>
-      <c r="C52" t="str">
-        <v>入侵</v>
-      </c>
-      <c r="D52" t="str">
-        <v>invasion(入侵)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>wake</v>
-      </c>
-      <c r="C53" t="str">
-        <v>唤醒</v>
-      </c>
-      <c r="D53" t="str">
-        <v>wake(唤醒)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>dream</v>
-      </c>
-      <c r="C54" t="str">
-        <v>梦想</v>
-      </c>
-      <c r="D54" t="str">
-        <v>dream(梦想)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>mechanics</v>
-      </c>
-      <c r="C55" t="str">
-        <v>力学</v>
-      </c>
-      <c r="D55" t="str">
-        <v>mechanics(力学)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>substance</v>
-      </c>
-      <c r="C56" t="str">
         <v>物质</v>
-      </c>
-      <c r="D56" t="str">
-        <v>substance(物质)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>